--- a/check/giayphep.xlsx
+++ b/check/giayphep.xlsx
@@ -19,10 +19,10 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
